--- a/data/fuente_formulario.xlsx
+++ b/data/fuente_formulario.xlsx
@@ -12,7 +12,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="643">
+  <si>
+    <t>y el y el</t>
+  </si>
   <si>
     <t>Timestamp</t>
   </si>
@@ -1816,6 +1819,159 @@
   </si>
   <si>
     <t xml:space="preserve">Nada supongo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cesar Morales Mora </t>
+  </si>
+  <si>
+    <t>11 Julio 1963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809-710-1743 </t>
+  </si>
+  <si>
+    <t>Desde el XIX ETC</t>
+  </si>
+  <si>
+    <t>XVII ETC</t>
+  </si>
+  <si>
+    <t>Servir</t>
+  </si>
+  <si>
+    <t>809 246 2374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con Dios </t>
+  </si>
+  <si>
+    <t>Ningunas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petra Yamina Morales </t>
+  </si>
+  <si>
+    <t>52, 19 de Octubre 1973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809 224 4482 </t>
+  </si>
+  <si>
+    <t>15 a 20</t>
+  </si>
+  <si>
+    <t>25, 2001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diferencia generacional con el resto del equipo </t>
+  </si>
+  <si>
+    <t>Naomi Santos Gomez</t>
+  </si>
+  <si>
+    <t>Reencuentro pasadia de Etecianos</t>
+  </si>
+  <si>
+    <t>Pre diabetes</t>
+  </si>
+  <si>
+    <t>Metformina y Sinvastina</t>
+  </si>
+  <si>
+    <t>Richard Dominguez, esposo, 809 502 8765</t>
+  </si>
+  <si>
+    <t>Escogida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha y lugar del retiro </t>
+  </si>
+  <si>
+    <t>Zahir Valoy</t>
+  </si>
+  <si>
+    <t>19años - 7 de junio del 2007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85 año 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espero conocer a los demás etc y servir de buena manera para este propósito </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miedo a ser rechazado socialmente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Que sienta, no </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rifa o torneo de alguna actividad en específico </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solangel Martínez, madre, 809-880-6698 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nada </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nelson Mariano Morales Aybar </t>
+  </si>
+  <si>
+    <t>33 años - 05 de enero de 1993</t>
+  </si>
+  <si>
+    <t>+1 809 914 4264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETC LV (55) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revivir gran parte de mi ETC desde otra perspectiva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No identifico algo en específico </t>
+  </si>
+  <si>
+    <t>Parmenia María Morales Aybar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrera 5k </t>
+  </si>
+  <si>
+    <t>María Gisela Aybar Jorge, madre, 8098182213</t>
+  </si>
+  <si>
+    <t>Cristopher Jimenez</t>
+  </si>
+  <si>
+    <t>25 años - 3 de enero 2001</t>
+  </si>
+  <si>
+    <t>77, 2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La experiencia del dar lo ya recibido </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desequilibrio constante en mi disciplina y consistencia en cuanto a la participación en comunidad y desarrollo personal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelidad, responsabilidad </t>
+  </si>
+  <si>
+    <t>Polvo y Aromas fuertes (rinitis alérgica)</t>
+  </si>
+  <si>
+    <t>Sonia Trinidad - Madre -8297870545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninguna por el momento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es mi primera vez participando </t>
   </si>
 </sst>
 </file>
@@ -1852,9 +2008,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1960,7 +2119,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:Y50" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:Y55" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="25">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Nombre completo" id="2"/>
@@ -2221,3020 +2380,3327 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>24</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>46173.44520590278</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="3">
+      <c r="E2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="4">
         <v>10.0</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="5">
         <v>522012.0</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="T2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="U2" s="3" t="s">
+      <c r="S2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="T2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="V2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="3" t="s">
-        <v>31</v>
+      <c r="W2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="6">
+      <c r="A3" s="7">
         <v>46173.608671875</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="K3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="S3" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="V3" s="7" t="s">
+      <c r="T3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="U3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="V3" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="W3" s="8" t="s">
         <v>51</v>
+      </c>
+      <c r="Y3" s="8" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>46173.61209277778</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="7">
+      <c r="E4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="8">
         <v>4.0</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" s="7" t="s">
+      <c r="J4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="T4" s="7" t="s">
+      <c r="R4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="U4" s="7" t="s">
+      <c r="T4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="V4" s="7" t="s">
+      <c r="U4" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="W4" s="7" t="s">
+      <c r="V4" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="X4" s="7" t="s">
+      <c r="W4" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="Y4" s="7" t="s">
+      <c r="X4" s="8" t="s">
         <v>66</v>
+      </c>
+      <c r="Y4" s="8" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>46173.61447730324</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="D5" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="8">
         <v>2.0</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" s="7" t="s">
+      <c r="J5" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="S5" s="7" t="s">
+      <c r="K5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="T5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="V5" s="7" t="s">
+      <c r="S5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="W5" s="7" t="s">
+      <c r="T5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="V5" s="8" t="s">
         <v>77</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>46173.61638340278</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="J6" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="K6" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="M6" s="7">
+      <c r="L6" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="M6" s="8">
         <v>18.0</v>
       </c>
-      <c r="N6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O6" s="7" t="s">
+      <c r="N6" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="P6" s="7">
+      <c r="O6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="P6" s="8">
         <v>18.0</v>
       </c>
-      <c r="Q6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="S6" s="7" t="s">
+      <c r="Q6" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="R6" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="T6" s="7" t="s">
+      <c r="S6" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="U6" s="7" t="s">
+      <c r="T6" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="V6" s="7" t="s">
+      <c r="U6" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="W6" s="7" t="s">
+      <c r="V6" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="X6" s="7" t="s">
+      <c r="W6" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="Y6" s="7" t="s">
-        <v>97</v>
+      <c r="X6" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y6" s="8" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>46173.61645018519</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="E7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="T7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V7" s="7" t="s">
+      <c r="I7" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="W7" s="7" t="s">
+      <c r="K7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V7" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="X7" s="7" t="s">
+      <c r="W7" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="Y7" s="7" t="s">
+      <c r="X7" s="8" t="s">
         <v>108</v>
+      </c>
+      <c r="Y7" s="8" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>46173.61825946759</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="D8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="8">
         <v>2.0</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <v>79.0</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" s="7" t="s">
+      <c r="H8" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R8" s="7" t="s">
+      <c r="J8" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="T8" s="7" t="s">
+      <c r="K8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R8" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="U8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V8" s="7" t="s">
+      <c r="S8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T8" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="W8" s="7" t="s">
+      <c r="U8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V8" s="8" t="s">
         <v>117</v>
+      </c>
+      <c r="W8" s="8" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <v>46173.625384583334</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="D9" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="8">
         <v>1.0</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="H9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="H9" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L9" s="7" t="s">
+      <c r="J9" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="K9" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="N9" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="R9" s="7" t="s">
+      <c r="M9" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="S9" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U9" s="7" t="s">
+      <c r="N9" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="V9" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="W9" s="7" t="s">
+      <c r="U9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V9" s="8" t="s">
         <v>129</v>
+      </c>
+      <c r="W9" s="8" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="6">
+      <c r="A10" s="7">
         <v>46173.63073379629</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="E10" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="H10" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L10" s="7" t="s">
+      <c r="J10" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="M10" s="7">
+      <c r="K10" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="M10" s="8">
         <v>21.0</v>
       </c>
-      <c r="N10" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="S10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="V10" s="7" t="s">
+      <c r="N10" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="R10" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="W10" s="7" t="s">
+      <c r="S10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="V10" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="X10" s="7" t="s">
+      <c r="W10" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Y10" s="7" t="s">
+      <c r="X10" s="8" t="s">
         <v>143</v>
+      </c>
+      <c r="Y10" s="8" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <v>46173.63178861111</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="D11" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="8">
         <v>1.0</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="H11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="I11" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="K11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R11" s="7" t="s">
+      <c r="J11" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="U11" s="7" t="s">
+      <c r="K11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R11" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="V11" s="7" t="s">
+      <c r="U11" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="W11" s="7" t="s">
+      <c r="V11" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="X11" s="7" t="s">
+      <c r="W11" s="8" t="s">
         <v>155</v>
+      </c>
+      <c r="X11" s="8" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="6">
+      <c r="A12" s="7">
         <v>46173.63194377314</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D12" s="7">
+      <c r="C12" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" s="8">
         <v>8.298019927E9</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E12" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="8">
         <v>1.0</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="8">
         <v>66.0</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J12" s="7" t="s">
+      <c r="H12" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R12" s="7" t="s">
+      <c r="J12" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="S12" s="7" t="s">
+      <c r="K12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R12" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="T12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V12" s="7" t="s">
+      <c r="S12" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="W12" s="7" t="s">
+      <c r="T12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V12" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="X12" s="7" t="s">
+      <c r="W12" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="Y12" s="7" t="s">
+      <c r="X12" s="8" t="s">
         <v>165</v>
+      </c>
+      <c r="Y12" s="8" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="6">
+      <c r="A13" s="7">
         <v>46173.64173805555</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="D13" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="8">
         <v>4.0</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="H13" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R13" s="7" t="s">
+      <c r="J13" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U13" s="7" t="s">
+      <c r="R13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="V13" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="W13" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="X13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y13" s="7" t="s">
+      <c r="S13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U13" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="V13" s="8" t="s">
         <v>174</v>
+      </c>
+      <c r="W13" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="X13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y13" s="8" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="6">
+      <c r="A14" s="7">
         <v>46173.64823626158</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F14" s="7">
+      <c r="D14" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="8">
         <v>3.0</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="H14" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L14" s="7" t="s">
+      <c r="J14" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="M14" s="7">
+      <c r="K14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="M14" s="8">
         <v>25.0</v>
       </c>
-      <c r="N14" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="R14" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="S14" s="7" t="s">
+      <c r="N14" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="R14" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="T14" s="7" t="s">
+      <c r="S14" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="U14" s="7" t="s">
+      <c r="T14" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="V14" s="7" t="s">
+      <c r="U14" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="W14" s="7" t="s">
+      <c r="V14" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="X14" s="7" t="s">
+      <c r="W14" s="8" t="s">
         <v>188</v>
+      </c>
+      <c r="X14" s="8" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="6">
+      <c r="A15" s="7">
         <v>46173.652789178246</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D15" s="7">
+      <c r="C15" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="8">
         <v>8.092636802E9</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="8">
         <v>4.0</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="H15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="H15" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="I15" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="K15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R15" s="7" t="s">
+      <c r="J15" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="S15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="T15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V15" s="7" t="s">
+      <c r="K15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R15" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="W15" s="7" t="s">
+      <c r="S15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V15" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="X15" s="7" t="s">
+      <c r="W15" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="Y15" s="7" t="s">
+      <c r="X15" s="8" t="s">
         <v>199</v>
+      </c>
+      <c r="Y15" s="8" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="6">
+      <c r="A16" s="7">
         <v>46173.65919825231</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="D16" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="8">
         <v>1.0</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="H16" s="7" t="s">
+      <c r="G16" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="H16" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="I16" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R16" s="7" t="s">
+      <c r="J16" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="S16" s="7" t="s">
+      <c r="K16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="T16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V16" s="7" t="s">
+      <c r="S16" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="W16" s="7" t="s">
+      <c r="T16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V16" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="X16" s="7" t="s">
+      <c r="W16" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="Y16" s="7" t="s">
+      <c r="X16" s="8" t="s">
         <v>212</v>
+      </c>
+      <c r="Y16" s="8" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="6">
+      <c r="A17" s="7">
         <v>46173.66321079861</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="D17" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="8">
         <v>2.0</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="8">
         <v>77.0</v>
       </c>
-      <c r="H17" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R17" s="7" t="s">
+      <c r="H17" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="T17" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="U17" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="V17" s="7" t="s">
+      <c r="K17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R17" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="W17" s="7" t="s">
+      <c r="S17" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="T17" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="V17" s="8" t="s">
         <v>219</v>
+      </c>
+      <c r="W17" s="8" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="6">
+      <c r="A18" s="7">
         <v>46173.720466412036</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="E18" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="G18" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="H18" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="I18" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="K18" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R18" s="7" t="s">
+      <c r="J18" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="S18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V18" s="7" t="s">
+      <c r="K18" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R18" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="W18" s="7" t="s">
+      <c r="S18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V18" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="X18" s="7" t="s">
+      <c r="W18" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="Y18" s="7" t="s">
+      <c r="X18" s="8" t="s">
         <v>232</v>
+      </c>
+      <c r="Y18" s="8" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="6">
+      <c r="A19" s="7">
         <v>46173.72640640046</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="E19" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="G19" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="H19" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="I19" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L19" s="7" t="s">
+      <c r="J19" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="M19" s="7">
+      <c r="K19" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M19" s="8">
         <v>32.0</v>
       </c>
-      <c r="N19" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O19" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="P19" s="7">
+      <c r="N19" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="P19" s="8">
         <v>33.0</v>
       </c>
-      <c r="Q19" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="R19" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="S19" s="7" t="s">
+      <c r="Q19" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="R19" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="T19" s="7" t="s">
+      <c r="S19" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="U19" s="7" t="s">
+      <c r="T19" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="V19" s="7" t="s">
+      <c r="U19" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="W19" s="7" t="s">
+      <c r="V19" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="X19" s="7" t="s">
+      <c r="W19" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="Y19" s="7" t="s">
+      <c r="X19" s="8" t="s">
         <v>250</v>
+      </c>
+      <c r="Y19" s="8" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="6">
+      <c r="A20" s="7">
         <v>46173.72855407407</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="C20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D20" s="7">
+      <c r="C20" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D20" s="8">
         <v>8.49864851E9</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="7">
+      <c r="E20" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="8">
         <v>4.0</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H20" s="7" t="s">
+      <c r="G20" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="H20" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="J20" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L20" s="7" t="s">
+      <c r="I20" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="M20" s="7">
+      <c r="J20" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="M20" s="8">
         <v>25.0</v>
       </c>
-      <c r="N20" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="P20" s="7">
+      <c r="N20" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="P20" s="8">
         <v>18.0</v>
       </c>
-      <c r="Q20" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="R20" s="7" t="s">
+      <c r="Q20" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="S20" s="7" t="s">
+      <c r="R20" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="T20" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U20" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="V20" s="7" t="s">
+      <c r="S20" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="W20" s="7" t="s">
+      <c r="T20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U20" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V20" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="X20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y20" s="7" t="s">
+      <c r="W20" s="8" t="s">
         <v>263</v>
+      </c>
+      <c r="X20" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y20" s="8" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="6">
+      <c r="A21" s="7">
         <v>46173.72886616898</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="7" t="s">
+      <c r="D21" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="E21" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="G21" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="H21" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="I21" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="K21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R21" s="7" t="s">
+      <c r="J21" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="S21" s="7" t="s">
+      <c r="K21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R21" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="T21" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U21" s="7" t="s">
+      <c r="S21" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="V21" s="7" t="s">
+      <c r="T21" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U21" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="W21" s="7" t="s">
+      <c r="V21" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="X21" s="7" t="s">
+      <c r="W21" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="Y21" s="7" t="s">
-        <v>277</v>
+      <c r="X21" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="Y21" s="8" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="6">
+      <c r="A22" s="7">
         <v>46173.745341041664</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="D22" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="8">
         <v>1.0</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="H22" s="7" t="s">
+      <c r="G22" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="H22" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="I22" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="K22" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R22" s="7" t="s">
+      <c r="J22" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="S22" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T22" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="V22" s="7" t="s">
+      <c r="K22" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R22" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="W22" s="7" t="s">
+      <c r="S22" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T22" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U22" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V22" s="8" t="s">
         <v>287</v>
+      </c>
+      <c r="W22" s="8" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="6">
+      <c r="A23" s="7">
         <v>46173.775271527775</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="C23" s="7" t="s">
+      <c r="B23" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="7">
+      <c r="D23" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="8">
         <v>2.0</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="H23" s="7" t="s">
+      <c r="G23" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="H23" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="I23" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="J23" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="S23" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T23" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="U23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="V23" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="W23" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y23" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="R23" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="S23" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="T23" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="U23" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="V23" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="W23" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="Y23" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="6">
+      <c r="A24" s="7">
         <v>46173.91046777778</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="C24" s="7">
+      <c r="B24" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C24" s="8">
         <v>27.0</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="8">
         <v>8.098826523E9</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="E24" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" s="8">
         <v>1.0</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="H24" s="7" t="s">
+      <c r="G24" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="H24" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="J24" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24" s="7" t="s">
+      <c r="I24" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="R24" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="S24" s="7" t="s">
+      <c r="K24" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R24" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="T24" s="7" t="s">
+      <c r="S24" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="U24" s="7" t="s">
+      <c r="T24" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="V24" s="7" t="s">
+      <c r="U24" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="W24" s="7" t="s">
+      <c r="V24" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="X24" s="7" t="s">
+      <c r="W24" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="Y24" s="7" t="s">
+      <c r="X24" s="8" t="s">
         <v>310</v>
+      </c>
+      <c r="Y24" s="8" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="6">
+      <c r="A25" s="7">
         <v>46173.92453238426</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="C25" s="7" t="s">
+      <c r="B25" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="D25" s="7">
+      <c r="C25" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D25" s="8">
         <v>8.299946731E9</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" s="7">
+      <c r="E25" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="8">
         <v>2.0</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="H25" s="7" t="s">
+      <c r="G25" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="H25" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="I25" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="K25" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L25" s="7" t="s">
+      <c r="J25" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="M25" s="7">
+      <c r="K25" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="M25" s="8">
         <v>27.0</v>
       </c>
-      <c r="N25" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="S25" s="7" t="s">
+      <c r="N25" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="R25" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="T25" s="7" t="s">
+      <c r="S25" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="U25" s="7" t="s">
+      <c r="T25" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="V25" s="7" t="s">
+      <c r="U25" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="W25" s="7" t="s">
+      <c r="V25" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="X25" s="7" t="s">
+      <c r="W25" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="Y25" s="7" t="s">
+      <c r="X25" s="8" t="s">
         <v>325</v>
+      </c>
+      <c r="Y25" s="8" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="6">
+      <c r="A26" s="7">
         <v>46173.92807015046</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="C26" s="7" t="s">
+      <c r="B26" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="D26" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="8">
         <v>1.0</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="H26" s="7" t="s">
+      <c r="G26" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="H26" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="J26" s="7" t="s">
+      <c r="I26" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="K26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R26" s="7" t="s">
+      <c r="J26" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="S26" s="7" t="s">
+      <c r="K26" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R26" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="T26" s="7" t="s">
+      <c r="S26" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="U26" s="7" t="s">
+      <c r="T26" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="V26" s="7" t="s">
+      <c r="U26" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="W26" s="7" t="s">
+      <c r="V26" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="X26" s="7" t="s">
+      <c r="W26" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="Y26" s="7" t="s">
+      <c r="X26" s="8" t="s">
         <v>340</v>
+      </c>
+      <c r="Y26" s="8" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="6">
+      <c r="A27" s="7">
         <v>46173.93182864583</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="C27" s="7" t="s">
+      <c r="B27" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="D27" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G27" s="7" t="s">
+      <c r="E27" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="F27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="I27" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J27" s="7" t="s">
+      <c r="H27" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="K27" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R27" s="7" t="s">
+      <c r="I27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="S27" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T27" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U27" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="V27" s="7" t="s">
+      <c r="K27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R27" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="W27" s="7" t="s">
+      <c r="S27" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T27" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U27" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="V27" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="X27" s="7" t="s">
+      <c r="W27" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="Y27" s="7" t="s">
+      <c r="X27" s="8" t="s">
         <v>352</v>
+      </c>
+      <c r="Y27" s="8" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="6">
+      <c r="A28" s="7">
         <v>46173.9439225463</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="C28" s="7" t="s">
+      <c r="B28" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="D28" s="7">
+      <c r="C28" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="D28" s="8">
         <v>8.299860995E9</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="E28" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="8">
         <v>9.0</v>
       </c>
-      <c r="G28" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="H28" s="7" t="s">
+      <c r="G28" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="I28" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J28" s="7" t="s">
+      <c r="H28" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="K28" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R28" s="7" t="s">
+      <c r="I28" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="S28" s="7" t="s">
+      <c r="K28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R28" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="T28" s="7" t="s">
+      <c r="S28" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="U28" s="7" t="s">
+      <c r="T28" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="V28" s="7" t="s">
+      <c r="U28" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="W28" s="7" t="s">
+      <c r="V28" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="X28" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y28" s="7" t="s">
+      <c r="W28" s="8" t="s">
         <v>364</v>
+      </c>
+      <c r="X28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y28" s="8" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="6">
+      <c r="A29" s="7">
         <v>46173.94976027778</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="C29" s="7" t="s">
+      <c r="B29" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="D29" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="F29" s="8">
         <v>3.0</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="H29" s="7" t="s">
+      <c r="G29" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="H29" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="I29" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="K29" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R29" s="7" t="s">
+      <c r="J29" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="S29" s="7" t="s">
+      <c r="K29" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R29" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="T29" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="U29" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="V29" s="7" t="s">
+      <c r="S29" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="W29" s="7" t="s">
+      <c r="T29" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="U29" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="V29" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="X29" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y29" s="7" t="s">
+      <c r="W29" s="8" t="s">
         <v>376</v>
+      </c>
+      <c r="X29" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="Y29" s="8" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="6">
+      <c r="A30" s="7">
         <v>46173.95904909722</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="C30" s="7" t="s">
+      <c r="B30" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="C30" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F30" s="7">
+      <c r="D30" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="8">
         <v>3.0</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="8">
         <v>55.0</v>
       </c>
-      <c r="H30" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="I30" s="7" t="s">
+      <c r="H30" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="I30" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="K30" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R30" s="7" t="s">
+      <c r="J30" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="S30" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="T30" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U30" s="7" t="s">
+      <c r="K30" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R30" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="V30" s="7" t="s">
+      <c r="S30" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T30" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U30" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="W30" s="7" t="s">
+      <c r="V30" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="X30" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y30" s="7" t="s">
-        <v>352</v>
+      <c r="W30" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="X30" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y30" s="8" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="6">
+      <c r="A31" s="7">
         <v>46173.96036144676</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="C31" s="7" t="s">
+      <c r="B31" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="D31" s="7">
+      <c r="C31" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="D31" s="8">
         <v>8.296101254E9</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F31" s="7">
+      <c r="E31" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="8">
         <v>2.0</v>
       </c>
-      <c r="G31" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="I31" s="7" t="s">
+      <c r="G31" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="H31" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="I31" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="K31" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L31" s="7" t="s">
+      <c r="J31" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="M31" s="7">
+      <c r="K31" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="M31" s="8">
         <v>23.0</v>
       </c>
-      <c r="N31" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="O31" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="P31" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q31" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="R31" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="S31" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T31" s="7" t="s">
+      <c r="N31" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="P31" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q31" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="R31" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="U31" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="V31" s="7" t="s">
+      <c r="S31" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T31" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="W31" s="7" t="s">
+      <c r="U31" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="V31" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="X31" s="7" t="s">
+      <c r="W31" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="Y31" s="7" t="s">
+      <c r="X31" s="8" t="s">
         <v>398</v>
+      </c>
+      <c r="Y31" s="8" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="6">
+      <c r="A32" s="7">
         <v>46173.995092303245</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="C32" s="7" t="s">
+      <c r="B32" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F32" s="7">
+      <c r="D32" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32" s="8">
         <v>0.0</v>
       </c>
-      <c r="G32" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="H32" s="7" t="s">
+      <c r="G32" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="H32" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="J32" s="7" t="s">
+      <c r="I32" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="K32" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L32" s="7" t="s">
+      <c r="J32" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="M32" s="7">
+      <c r="K32" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="M32" s="8">
         <v>25.0</v>
       </c>
-      <c r="N32" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="R32" s="7" t="s">
+      <c r="N32" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="S32" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="T32" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U32" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="V32" s="7" t="s">
+      <c r="R32" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="W32" s="7" t="s">
+      <c r="S32" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T32" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U32" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="V32" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="X32" s="7" t="s">
+      <c r="W32" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="Y32" s="7" t="s">
+      <c r="X32" s="8" t="s">
         <v>412</v>
+      </c>
+      <c r="Y32" s="8" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="6">
+      <c r="A33" s="7">
         <v>46174.022956319444</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="C33" s="7" t="s">
+      <c r="B33" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="C33" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" s="7" t="s">
+      <c r="D33" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="E33" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="G33" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="H33" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="K33" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="S33" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T33" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U33" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="V33" s="7" t="s">
+      <c r="I33" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="W33" s="7" t="s">
+      <c r="K33" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="S33" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T33" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U33" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V33" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="X33" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y33" s="7" t="s">
-        <v>31</v>
+      <c r="W33" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="X33" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y33" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="6">
+      <c r="A34" s="7">
         <v>46174.383722812505</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="C34" s="7" t="s">
+      <c r="B34" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="C34" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F34" s="7">
+      <c r="D34" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" s="8">
         <v>5.0</v>
       </c>
-      <c r="G34" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="H34" s="7" t="s">
+      <c r="G34" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="H34" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="I34" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="K34" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R34" s="7" t="s">
+      <c r="J34" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="S34" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="T34" s="7" t="s">
+      <c r="K34" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R34" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="S34" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="U34" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="V34" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="W34" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="X34" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y34" s="7" t="s">
-        <v>48</v>
+      <c r="T34" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U34" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="V34" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="W34" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="X34" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y34" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="6">
+      <c r="A35" s="7">
         <v>46174.38468366898</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="C35" s="7" t="s">
+      <c r="B35" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="D35" s="7">
+      <c r="C35" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="D35" s="8">
         <v>8.09860763E9</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="G35" s="7">
+      <c r="E35" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="G35" s="8">
         <v>45.0</v>
       </c>
-      <c r="H35" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="I35" s="7" t="s">
+      <c r="H35" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="I35" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="K35" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R35" s="7" t="s">
+      <c r="J35" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="S35" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T35" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U35" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="V35" s="7" t="s">
+      <c r="K35" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R35" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="W35" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="X35" s="7" t="s">
+      <c r="S35" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T35" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U35" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V35" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="Y35" s="7" t="s">
+      <c r="W35" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="X35" s="8" t="s">
         <v>439</v>
+      </c>
+      <c r="Y35" s="8" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="6">
+      <c r="A36" s="7">
         <v>46174.421322002316</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="C36" s="7" t="s">
+      <c r="B36" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="D36" s="7">
+      <c r="C36" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="D36" s="8">
         <v>8.292644176E9</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="G36" s="7" t="s">
+      <c r="E36" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="F36" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="G36" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="H36" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="I36" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="K36" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R36" s="7" t="s">
+      <c r="J36" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="S36" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="T36" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U36" s="7" t="s">
+      <c r="K36" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R36" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="S36" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="V36" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="W36" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="X36" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y36" s="7" t="s">
-        <v>188</v>
+      <c r="T36" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U36" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V36" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="W36" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="X36" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y36" s="8" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="6">
+      <c r="A37" s="7">
         <v>46174.422981724536</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="C37" s="7" t="s">
+      <c r="B37" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D37" s="7">
+      <c r="C37" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="D37" s="8">
         <v>8.299180666E9</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="G37" s="7" t="s">
+      <c r="E37" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="G37" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="J37" s="7" t="s">
+      <c r="H37" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="K37" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="S37" s="7" t="s">
+      <c r="J37" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="T37" s="7" t="s">
+      <c r="K37" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S37" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="U37" s="7" t="s">
+      <c r="T37" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="V37" s="7" t="s">
+      <c r="U37" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="W37" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="Y37" s="7" t="s">
+      <c r="V37" s="8" t="s">
         <v>459</v>
+      </c>
+      <c r="W37" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="Y37" s="8" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="6">
+      <c r="A38" s="7">
         <v>46174.48594907408</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="C38" s="7" t="s">
+      <c r="B38" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="C38" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="E38" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F38" s="7" t="s">
+      <c r="D38" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="G38" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="H38" s="7" t="s">
+      <c r="E38" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="G38" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="H38" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="J38" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="K38" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R38" s="7" t="s">
+      <c r="I38" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="S38" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="T38" s="7" t="s">
+      <c r="J38" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R38" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="U38" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V38" s="7" t="s">
+      <c r="S38" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T38" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="W38" s="7" t="s">
+      <c r="U38" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V38" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="X38" s="7" t="s">
+      <c r="W38" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="Y38" s="7" t="s">
+      <c r="X38" s="8" t="s">
         <v>471</v>
+      </c>
+      <c r="Y38" s="8" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="6">
+      <c r="A39" s="7">
         <v>46174.551638159726</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="C39" s="7" t="s">
+      <c r="B39" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="C39" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F39" s="7">
+      <c r="D39" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="8">
         <v>2.0</v>
       </c>
-      <c r="G39" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="H39" s="7" t="s">
+      <c r="G39" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="K39" s="7" t="s">
+      <c r="H39" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R39" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="S39" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T39" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U39" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V39" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="W39" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="X39" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="Y39" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="R39" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="S39" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T39" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U39" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="V39" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="W39" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="X39" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="Y39" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="6">
+      <c r="A40" s="7">
         <v>46174.78047268519</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="C40" s="7" t="s">
+      <c r="B40" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="C40" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G40" s="7">
+      <c r="D40" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40" s="8">
         <v>70.0</v>
       </c>
-      <c r="H40" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J40" s="7" t="s">
+      <c r="H40" s="8" t="s">
         <v>484</v>
       </c>
-      <c r="K40" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L40" s="7" t="s">
+      <c r="I40" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J40" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="M40" s="7">
+      <c r="K40" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="M40" s="8">
         <v>22.0</v>
       </c>
-      <c r="N40" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="R40" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="S40" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T40" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U40" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="V40" s="7" t="s">
+      <c r="N40" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="R40" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="W40" s="7" t="s">
+      <c r="S40" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T40" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U40" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V40" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="X40" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y40" s="7" t="s">
-        <v>31</v>
+      <c r="W40" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="X40" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y40" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="6">
+      <c r="A41" s="7">
         <v>46174.80301689815</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="C41" s="7" t="s">
+      <c r="B41" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="D41" s="7">
+      <c r="C41" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="D41" s="8">
         <v>8.098636434E9</v>
       </c>
-      <c r="E41" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F41" s="7">
+      <c r="E41" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F41" s="8">
         <v>5.0</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="8">
         <v>70.0</v>
       </c>
-      <c r="H41" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="I41" s="7" t="s">
+      <c r="H41" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="J41" s="7" t="s">
+      <c r="I41" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="K41" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R41" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="S41" s="7" t="s">
+      <c r="J41" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="T41" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U41" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="V41" s="7" t="s">
+      <c r="K41" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R41" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="S41" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="W41" s="7" t="s">
+      <c r="T41" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U41" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V41" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="X41" s="7" t="s">
+      <c r="W41" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="Y41" s="7" t="s">
+      <c r="X41" s="8" t="s">
         <v>498</v>
+      </c>
+      <c r="Y41" s="8" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="6">
+      <c r="A42" s="7">
         <v>46175.00809928241</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="C42" s="7" t="s">
+      <c r="B42" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="C42" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F42" s="7">
+      <c r="D42" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F42" s="8">
         <v>8.0</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="8">
         <v>62.0</v>
       </c>
-      <c r="H42" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="J42" s="7" t="s">
+      <c r="H42" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="K42" s="7" t="s">
+      <c r="I42" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R42" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="S42" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="T42" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U42" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V42" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="W42" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="X42" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="Y42" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="R42" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="S42" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="T42" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U42" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="V42" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="W42" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="X42" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y42" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="6">
+      <c r="A43" s="7">
         <v>46175.839562407404</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="C43" s="7" t="s">
+      <c r="B43" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="C43" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="E43" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F43" s="7">
+      <c r="D43" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F43" s="8">
         <v>0.0</v>
       </c>
-      <c r="G43" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="H43" s="7" t="s">
+      <c r="G43" s="8" t="s">
         <v>511</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="H43" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="I43" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="K43" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="S43" s="7" t="s">
+      <c r="J43" s="8" t="s">
         <v>514</v>
       </c>
-      <c r="V43" s="7" t="s">
+      <c r="K43" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S43" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="W43" s="7" t="s">
+      <c r="V43" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="Y43" s="7" t="s">
+      <c r="W43" s="8" t="s">
         <v>517</v>
+      </c>
+      <c r="Y43" s="8" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="6">
+      <c r="A44" s="7">
         <v>46175.84526743056</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="C44" s="7" t="s">
+      <c r="B44" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="D44" s="7">
+      <c r="C44" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="D44" s="8">
         <v>8.494062313E9</v>
       </c>
-      <c r="E44" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="G44" s="7" t="s">
+      <c r="E44" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F44" s="8" t="s">
         <v>521</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="G44" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="I44" s="7" t="s">
+      <c r="H44" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="J44" s="7" t="s">
+      <c r="I44" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="K44" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L44" s="7" t="s">
+      <c r="J44" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="M44" s="7">
+      <c r="K44" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="M44" s="8">
         <v>18.0</v>
       </c>
-      <c r="N44" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O44" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="P44" s="7">
+      <c r="N44" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="O44" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="P44" s="8">
         <v>18.0</v>
       </c>
-      <c r="Q44" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="R44" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="S44" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T44" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U44" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V44" s="7" t="s">
+      <c r="Q44" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="R44" s="8" t="s">
         <v>528</v>
       </c>
-      <c r="W44" s="7" t="s">
+      <c r="S44" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T44" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U44" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V44" s="8" t="s">
         <v>529</v>
       </c>
-      <c r="X44" s="7" t="s">
+      <c r="W44" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="Y44" s="7" t="s">
+      <c r="X44" s="8" t="s">
         <v>531</v>
+      </c>
+      <c r="Y44" s="8" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="6">
+      <c r="A45" s="7">
         <v>46175.93678149306</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="C45" s="7" t="s">
+      <c r="B45" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="D45" s="7">
+      <c r="C45" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="D45" s="8">
         <v>8.298639956E9</v>
       </c>
-      <c r="E45" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F45" s="7">
+      <c r="E45" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" s="8">
         <v>3.0</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="8">
         <v>66.0</v>
       </c>
-      <c r="H45" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J45" s="7" t="s">
+      <c r="H45" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="K45" s="7" t="s">
+      <c r="I45" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="R45" s="7" t="s">
+      <c r="J45" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="S45" s="7" t="s">
+      <c r="K45" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R45" s="8" t="s">
         <v>537</v>
       </c>
-      <c r="T45" s="7" t="s">
+      <c r="S45" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="U45" s="7" t="s">
+      <c r="T45" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="V45" s="7" t="s">
+      <c r="U45" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="W45" s="7" t="s">
+      <c r="V45" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="X45" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y45" s="7" t="s">
+      <c r="W45" s="8" t="s">
         <v>542</v>
+      </c>
+      <c r="X45" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y45" s="8" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="6">
+      <c r="A46" s="7">
         <v>46175.973643888894</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="C46" s="7" t="s">
+      <c r="B46" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="C46" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="E46" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F46" s="7" t="s">
+      <c r="D46" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="G46" s="7">
+      <c r="E46" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="G46" s="8">
         <v>55.0</v>
       </c>
-      <c r="H46" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="I46" s="7" t="s">
+      <c r="H46" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="J46" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K46" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R46" s="7" t="s">
+      <c r="I46" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="S46" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="T46" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U46" s="7" t="s">
+      <c r="J46" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R46" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="S46" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="V46" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="W46" s="7" t="s">
-        <v>64</v>
+      <c r="T46" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U46" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V46" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="W46" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="6">
+      <c r="A47" s="7">
         <v>46175.97970467593</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="D47" s="7">
+      <c r="B47" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="D47" s="8">
         <v>8.295876445E9</v>
       </c>
-      <c r="E47" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F47" s="7">
+      <c r="E47" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="8">
         <v>9.0</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="8">
         <v>55.0</v>
       </c>
-      <c r="H47" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K47" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R47" s="7" t="s">
+      <c r="H47" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I47" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="S47" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="T47" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U47" s="7" t="s">
+      <c r="J47" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R47" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="S47" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="V47" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="W47" s="7" t="s">
+      <c r="T47" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U47" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V47" s="8" t="s">
         <v>555</v>
+      </c>
+      <c r="W47" s="8" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="6">
+      <c r="A48" s="7">
         <v>46177.92771297454</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>556</v>
-      </c>
-      <c r="C48" s="7" t="s">
+      <c r="B48" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="D48" s="7">
+      <c r="C48" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="D48" s="8">
         <v>8.29933023E9</v>
       </c>
-      <c r="E48" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G48" s="7" t="s">
+      <c r="E48" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="F48" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="I48" s="7" t="s">
+      <c r="H48" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="J48" s="7" t="s">
+      <c r="I48" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="K48" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L48" s="7" t="s">
+      <c r="J48" s="8" t="s">
         <v>563</v>
       </c>
-      <c r="M48" s="7">
+      <c r="K48" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="M48" s="8">
         <v>20.0</v>
       </c>
-      <c r="N48" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O48" s="7" t="s">
-        <v>564</v>
-      </c>
-      <c r="P48" s="7">
+      <c r="N48" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="O48" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="P48" s="8">
         <v>20.0</v>
       </c>
-      <c r="Q48" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="S48" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="T48" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U48" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V48" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="W48" s="7" t="s">
-        <v>386</v>
+      <c r="Q48" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="S48" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T48" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U48" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V48" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="W48" s="8" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="6">
+      <c r="A49" s="7">
         <v>46180.74766324074</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="C49" s="7" t="s">
+      <c r="B49" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="C49" s="8" t="s">
         <v>568</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G49" s="7" t="s">
+      <c r="D49" s="8" t="s">
         <v>569</v>
       </c>
-      <c r="H49" s="7" t="s">
+      <c r="E49" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49" s="8" t="s">
         <v>570</v>
       </c>
-      <c r="I49" s="7" t="s">
+      <c r="H49" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="J49" s="7" t="s">
+      <c r="I49" s="8" t="s">
         <v>572</v>
       </c>
-      <c r="K49" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R49" s="7" t="s">
+      <c r="J49" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="S49" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="T49" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U49" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V49" s="7" t="s">
+      <c r="K49" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R49" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="W49" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="X49" s="7" t="s">
+      <c r="S49" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T49" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U49" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V49" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="Y49" s="7" t="s">
+      <c r="W49" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="X49" s="8" t="s">
         <v>576</v>
+      </c>
+      <c r="Y49" s="8" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="6">
+      <c r="A50" s="7">
         <v>46183.37951251157</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="C50" s="7" t="s">
+      <c r="B50" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="C50" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="E50" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="G50" s="7" t="s">
+      <c r="D50" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="H50" s="7" t="s">
+      <c r="E50" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="G50" s="8" t="s">
         <v>581</v>
       </c>
-      <c r="I50" s="7" t="s">
+      <c r="H50" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="N50" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="R50" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="S50" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="T50" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="U50" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V50" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="W50" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="X50" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y50" s="8" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="A51" s="7">
+        <v>46186.90106991898</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R51" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="S51" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="T51" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="U51" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="V51" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="W51" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="X51" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="Y51" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="7">
+        <v>46187.677740694446</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="M52" s="8">
+        <v>18.0</v>
+      </c>
+      <c r="N52" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="R52" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="T52" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="U52" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="V52" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="W52" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="X52" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="Y52" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="7">
+        <v>46202.8890624537</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D53" s="8">
+        <v>8.49460103E9</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F53" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R53" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="S53" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T53" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U53" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="V53" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="W53" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="X53" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y53" s="8" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="7">
+        <v>46207.808178067135</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="M54" s="8">
+        <v>27.0</v>
+      </c>
+      <c r="N54" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="R54" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="S54" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T54" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U54" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V54" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="W54" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="X54" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y54" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="7">
+        <v>46210.63799015046</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="D55" s="8">
+        <v>8.098828282E9</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R55" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J50" s="7" t="s">
-        <v>582</v>
-      </c>
-      <c r="K50" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L50" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="M50" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="N50" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="R50" s="7" t="s">
-        <v>585</v>
-      </c>
-      <c r="S50" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="T50" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="U50" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="V50" s="7" t="s">
-        <v>588</v>
-      </c>
-      <c r="W50" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="X50" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="Y50" s="7" t="s">
-        <v>590</v>
+      <c r="S55" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="T55" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U55" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V55" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="W55" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="X55" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="Y55" s="8" t="s">
+        <v>642</v>
       </c>
     </row>
   </sheetData>
@@ -5251,7 +5717,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>